--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3880" uniqueCount="1213">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3367 +207,3424 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-02-25</t>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>1160613.179313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
   </si>
   <si>
     <t>1121261.858063</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2024-01-12</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7199,7 +7256,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E550"/>
+  <dimension ref="A1:E564"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16546,10 +16603,248 @@
         <v>521</v>
       </c>
       <c r="D550" t="s">
-        <v>61</v>
+        <v>1181</v>
       </c>
       <c r="E550" t="s">
         <v>1180</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="s">
+        <v>145</v>
+      </c>
+      <c r="B551" t="s">
+        <v>435</v>
+      </c>
+      <c r="C551" t="s">
+        <v>521</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E551" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="s">
+        <v>145</v>
+      </c>
+      <c r="B552" t="s">
+        <v>435</v>
+      </c>
+      <c r="C552" t="s">
+        <v>521</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E552" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="s">
+        <v>145</v>
+      </c>
+      <c r="B553" t="s">
+        <v>435</v>
+      </c>
+      <c r="C553" t="s">
+        <v>521</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E553" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="s">
+        <v>145</v>
+      </c>
+      <c r="B554" t="s">
+        <v>435</v>
+      </c>
+      <c r="C554" t="s">
+        <v>521</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E554" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="s">
+        <v>145</v>
+      </c>
+      <c r="B555" t="s">
+        <v>435</v>
+      </c>
+      <c r="C555" t="s">
+        <v>521</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E555" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="s">
+        <v>145</v>
+      </c>
+      <c r="B556" t="s">
+        <v>435</v>
+      </c>
+      <c r="C556" t="s">
+        <v>521</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E556" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="s">
+        <v>145</v>
+      </c>
+      <c r="B557" t="s">
+        <v>435</v>
+      </c>
+      <c r="C557" t="s">
+        <v>521</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E557" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="s">
+        <v>893</v>
+      </c>
+      <c r="B558" t="s">
+        <v>435</v>
+      </c>
+      <c r="C558" t="s">
+        <v>521</v>
+      </c>
+      <c r="D558" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E558" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="s">
+        <v>893</v>
+      </c>
+      <c r="B559" t="s">
+        <v>435</v>
+      </c>
+      <c r="C559" t="s">
+        <v>521</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E559" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="s">
+        <v>893</v>
+      </c>
+      <c r="B560" t="s">
+        <v>435</v>
+      </c>
+      <c r="C560" t="s">
+        <v>521</v>
+      </c>
+      <c r="D560" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E560" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B561" t="s">
+        <v>522</v>
+      </c>
+      <c r="C561" t="s">
+        <v>521</v>
+      </c>
+      <c r="D561" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E561" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B562" t="s">
+        <v>522</v>
+      </c>
+      <c r="C562" t="s">
+        <v>521</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E562" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B563" t="s">
+        <v>522</v>
+      </c>
+      <c r="C563" t="s">
+        <v>521</v>
+      </c>
+      <c r="D563" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E563" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B564" t="s">
+        <v>522</v>
+      </c>
+      <c r="C564" t="s">
+        <v>521</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E564" t="s">
+        <v>1183</v>
       </c>
     </row>
   </sheetData>
@@ -16564,13 +16859,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -16578,13 +16873,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -16592,13 +16887,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -16606,13 +16901,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -16620,13 +16915,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -16634,13 +16929,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -16648,13 +16943,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -16662,13 +16957,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -16676,13 +16971,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -16700,13 +16995,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -16717,13 +17012,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -16734,13 +17029,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -16751,13 +17046,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -16768,13 +17063,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -16785,13 +17080,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1190</v>
+        <v>1209</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -16802,13 +17097,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1191</v>
+        <v>1210</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -16819,13 +17114,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1192</v>
+        <v>1211</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -16836,13 +17131,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1193</v>
+        <v>1212</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3880" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3890" uniqueCount="1216">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,10 +207,10 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>1160613.179313</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>1166283.496813</t>
   </si>
   <si>
     <t>utkarsh</t>
@@ -3625,6 +3625,15 @@
   </si>
   <si>
     <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7256,7 +7265,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E564"/>
+  <dimension ref="A1:E566"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16845,6 +16854,40 @@
       </c>
       <c r="E564" t="s">
         <v>1183</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="s">
+        <v>145</v>
+      </c>
+      <c r="B565" t="s">
+        <v>435</v>
+      </c>
+      <c r="C565" t="s">
+        <v>521</v>
+      </c>
+      <c r="D565" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E565" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="s">
+        <v>145</v>
+      </c>
+      <c r="B566" t="s">
+        <v>435</v>
+      </c>
+      <c r="C566" t="s">
+        <v>521</v>
+      </c>
+      <c r="D566" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E566" t="s">
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -16859,13 +16902,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -16873,13 +16916,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -16887,13 +16930,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -16901,13 +16944,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -16915,13 +16958,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -16929,13 +16972,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -16943,13 +16986,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -16957,13 +17000,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -16971,13 +17014,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -16995,13 +17038,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17012,13 +17055,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17029,13 +17072,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17046,13 +17089,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17063,13 +17106,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17080,13 +17123,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17097,13 +17140,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17114,13 +17157,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17131,13 +17174,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3890" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="1225">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,10 +207,10 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>1166283.496813</t>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
   </si>
   <si>
     <t>utkarsh</t>
@@ -3634,6 +3634,33 @@
   </si>
   <si>
     <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7265,7 +7292,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E566"/>
+  <dimension ref="A1:E576"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16888,6 +16915,176 @@
       </c>
       <c r="E566" t="s">
         <v>1201</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="s">
+        <v>145</v>
+      </c>
+      <c r="B567" t="s">
+        <v>435</v>
+      </c>
+      <c r="C567" t="s">
+        <v>521</v>
+      </c>
+      <c r="D567" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E567" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="s">
+        <v>145</v>
+      </c>
+      <c r="B568" t="s">
+        <v>435</v>
+      </c>
+      <c r="C568" t="s">
+        <v>521</v>
+      </c>
+      <c r="D568" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E568" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="s">
+        <v>145</v>
+      </c>
+      <c r="B569" t="s">
+        <v>435</v>
+      </c>
+      <c r="C569" t="s">
+        <v>521</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E569" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="s">
+        <v>145</v>
+      </c>
+      <c r="B570" t="s">
+        <v>435</v>
+      </c>
+      <c r="C570" t="s">
+        <v>521</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E570" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="s">
+        <v>145</v>
+      </c>
+      <c r="B571" t="s">
+        <v>435</v>
+      </c>
+      <c r="C571" t="s">
+        <v>521</v>
+      </c>
+      <c r="D571" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E571" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="s">
+        <v>145</v>
+      </c>
+      <c r="B572" t="s">
+        <v>435</v>
+      </c>
+      <c r="C572" t="s">
+        <v>521</v>
+      </c>
+      <c r="D572" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E572" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="s">
+        <v>145</v>
+      </c>
+      <c r="B573" t="s">
+        <v>435</v>
+      </c>
+      <c r="C573" t="s">
+        <v>521</v>
+      </c>
+      <c r="D573" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E573" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="s">
+        <v>145</v>
+      </c>
+      <c r="B574" t="s">
+        <v>435</v>
+      </c>
+      <c r="C574" t="s">
+        <v>521</v>
+      </c>
+      <c r="D574" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E574" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="s">
+        <v>145</v>
+      </c>
+      <c r="B575" t="s">
+        <v>435</v>
+      </c>
+      <c r="C575" t="s">
+        <v>521</v>
+      </c>
+      <c r="D575" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E575" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="s">
+        <v>145</v>
+      </c>
+      <c r="B576" t="s">
+        <v>435</v>
+      </c>
+      <c r="C576" t="s">
+        <v>521</v>
+      </c>
+      <c r="D576" t="s">
+        <v>61</v>
+      </c>
+      <c r="E576" t="s">
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -16902,13 +17099,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -16916,13 +17113,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -16930,13 +17127,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -16944,13 +17141,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -16958,13 +17155,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -16972,13 +17169,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -16986,13 +17183,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17000,13 +17197,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17014,13 +17211,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17038,13 +17235,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17055,13 +17252,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17072,13 +17269,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17089,13 +17286,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17106,13 +17303,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17123,13 +17320,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17140,13 +17337,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17157,13 +17354,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17174,13 +17371,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3955" uniqueCount="1230">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3460 +207,3475 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-03-17</t>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
   </si>
   <si>
     <t>1196783.496813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2024-01-12</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7292,7 +7307,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E576"/>
+  <dimension ref="A1:E579"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -17081,10 +17096,61 @@
         <v>521</v>
       </c>
       <c r="D576" t="s">
-        <v>61</v>
+        <v>1212</v>
       </c>
       <c r="E576" t="s">
         <v>1211</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="s">
+        <v>145</v>
+      </c>
+      <c r="B577" t="s">
+        <v>435</v>
+      </c>
+      <c r="C577" t="s">
+        <v>521</v>
+      </c>
+      <c r="D577" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E577" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="s">
+        <v>145</v>
+      </c>
+      <c r="B578" t="s">
+        <v>435</v>
+      </c>
+      <c r="C578" t="s">
+        <v>521</v>
+      </c>
+      <c r="D578" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E578" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="s">
+        <v>145</v>
+      </c>
+      <c r="B579" t="s">
+        <v>435</v>
+      </c>
+      <c r="C579" t="s">
+        <v>521</v>
+      </c>
+      <c r="D579" t="s">
+        <v>61</v>
+      </c>
+      <c r="E579" t="s">
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
@@ -17099,13 +17165,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -17113,13 +17179,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -17127,13 +17193,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -17141,13 +17207,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -17155,13 +17221,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -17169,13 +17235,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -17183,13 +17249,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17197,13 +17263,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17211,13 +17277,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17235,13 +17301,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17252,13 +17318,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17269,13 +17335,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17286,13 +17352,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17303,13 +17369,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17320,13 +17386,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17337,13 +17403,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17354,13 +17420,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17371,13 +17437,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3955" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="1243">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3475 +207,3514 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-03-24</t>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>1248681.746813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
   </si>
   <si>
     <t>1220074.996813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2024-01-12</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
     <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7307,7 +7346,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E579"/>
+  <dimension ref="A1:E589"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -17147,10 +17186,180 @@
         <v>521</v>
       </c>
       <c r="D579" t="s">
-        <v>61</v>
+        <v>1216</v>
       </c>
       <c r="E579" t="s">
-        <v>1216</v>
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="s">
+        <v>145</v>
+      </c>
+      <c r="B580" t="s">
+        <v>435</v>
+      </c>
+      <c r="C580" t="s">
+        <v>521</v>
+      </c>
+      <c r="D580" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E580" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="s">
+        <v>145</v>
+      </c>
+      <c r="B581" t="s">
+        <v>435</v>
+      </c>
+      <c r="C581" t="s">
+        <v>521</v>
+      </c>
+      <c r="D581" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E581" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="s">
+        <v>145</v>
+      </c>
+      <c r="B582" t="s">
+        <v>435</v>
+      </c>
+      <c r="C582" t="s">
+        <v>521</v>
+      </c>
+      <c r="D582" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E582" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="s">
+        <v>145</v>
+      </c>
+      <c r="B583" t="s">
+        <v>435</v>
+      </c>
+      <c r="C583" t="s">
+        <v>521</v>
+      </c>
+      <c r="D583" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E583" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="s">
+        <v>145</v>
+      </c>
+      <c r="B584" t="s">
+        <v>435</v>
+      </c>
+      <c r="C584" t="s">
+        <v>521</v>
+      </c>
+      <c r="D584" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E584" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="s">
+        <v>145</v>
+      </c>
+      <c r="B585" t="s">
+        <v>435</v>
+      </c>
+      <c r="C585" t="s">
+        <v>521</v>
+      </c>
+      <c r="D585" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E585" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="s">
+        <v>145</v>
+      </c>
+      <c r="B586" t="s">
+        <v>435</v>
+      </c>
+      <c r="C586" t="s">
+        <v>521</v>
+      </c>
+      <c r="D586" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E586" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="s">
+        <v>145</v>
+      </c>
+      <c r="B587" t="s">
+        <v>435</v>
+      </c>
+      <c r="C587" t="s">
+        <v>521</v>
+      </c>
+      <c r="D587" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E587" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="s">
+        <v>145</v>
+      </c>
+      <c r="B588" t="s">
+        <v>435</v>
+      </c>
+      <c r="C588" t="s">
+        <v>521</v>
+      </c>
+      <c r="D588" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E588" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="s">
+        <v>145</v>
+      </c>
+      <c r="B589" t="s">
+        <v>435</v>
+      </c>
+      <c r="C589" t="s">
+        <v>521</v>
+      </c>
+      <c r="D589" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E589" t="s">
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -17165,13 +17374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -17179,13 +17388,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -17193,13 +17402,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -17207,13 +17416,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -17221,13 +17430,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -17235,13 +17444,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -17249,13 +17458,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17263,13 +17472,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17277,13 +17486,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17301,13 +17510,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17318,13 +17527,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17335,13 +17544,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17352,13 +17561,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17369,13 +17578,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17386,13 +17595,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17403,13 +17612,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17420,13 +17629,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17437,13 +17646,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="1249">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,10 +207,10 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>1248681.746813</t>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
   </si>
   <si>
     <t>utkarsh</t>
@@ -3715,6 +3715,24 @@
   </si>
   <si>
     <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7346,7 +7364,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E589"/>
+  <dimension ref="A1:E593"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -17360,6 +17378,74 @@
       </c>
       <c r="E589" t="s">
         <v>1227</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B590" t="s">
+        <v>522</v>
+      </c>
+      <c r="C590" t="s">
+        <v>521</v>
+      </c>
+      <c r="D590" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E590" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="s">
+        <v>630</v>
+      </c>
+      <c r="B591" t="s">
+        <v>522</v>
+      </c>
+      <c r="C591" t="s">
+        <v>521</v>
+      </c>
+      <c r="D591" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E591" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="s">
+        <v>630</v>
+      </c>
+      <c r="B592" t="s">
+        <v>522</v>
+      </c>
+      <c r="C592" t="s">
+        <v>521</v>
+      </c>
+      <c r="D592" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E592" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="s">
+        <v>630</v>
+      </c>
+      <c r="B593" t="s">
+        <v>522</v>
+      </c>
+      <c r="C593" t="s">
+        <v>521</v>
+      </c>
+      <c r="D593" t="s">
+        <v>61</v>
+      </c>
+      <c r="E593" t="s">
+        <v>1234</v>
       </c>
     </row>
   </sheetData>
@@ -17374,13 +17460,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -17388,13 +17474,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -17402,13 +17488,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -17416,13 +17502,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -17430,13 +17516,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -17444,13 +17530,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -17458,13 +17544,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17472,13 +17558,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17486,13 +17572,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17510,13 +17596,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17527,13 +17613,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17544,13 +17630,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17561,13 +17647,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17578,13 +17664,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17595,13 +17681,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17612,13 +17698,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17629,13 +17715,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17646,13 +17732,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="1263">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3532 +207,3574 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-04-07</t>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
   </si>
   <si>
     <t>1230601.739613</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2024-01-12</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7364,7 +7406,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E593"/>
+  <dimension ref="A1:E603"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -17442,10 +17484,180 @@
         <v>521</v>
       </c>
       <c r="D593" t="s">
-        <v>61</v>
+        <v>1236</v>
       </c>
       <c r="E593" t="s">
         <v>1234</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="s">
+        <v>145</v>
+      </c>
+      <c r="B594" t="s">
+        <v>435</v>
+      </c>
+      <c r="C594" t="s">
+        <v>521</v>
+      </c>
+      <c r="D594" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E594" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="s">
+        <v>145</v>
+      </c>
+      <c r="B595" t="s">
+        <v>435</v>
+      </c>
+      <c r="C595" t="s">
+        <v>521</v>
+      </c>
+      <c r="D595" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E595" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="s">
+        <v>145</v>
+      </c>
+      <c r="B596" t="s">
+        <v>435</v>
+      </c>
+      <c r="C596" t="s">
+        <v>521</v>
+      </c>
+      <c r="D596" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E596" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="s">
+        <v>145</v>
+      </c>
+      <c r="B597" t="s">
+        <v>435</v>
+      </c>
+      <c r="C597" t="s">
+        <v>521</v>
+      </c>
+      <c r="D597" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E597" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="s">
+        <v>145</v>
+      </c>
+      <c r="B598" t="s">
+        <v>435</v>
+      </c>
+      <c r="C598" t="s">
+        <v>521</v>
+      </c>
+      <c r="D598" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E598" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="s">
+        <v>145</v>
+      </c>
+      <c r="B599" t="s">
+        <v>435</v>
+      </c>
+      <c r="C599" t="s">
+        <v>521</v>
+      </c>
+      <c r="D599" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E599" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="s">
+        <v>145</v>
+      </c>
+      <c r="B600" t="s">
+        <v>435</v>
+      </c>
+      <c r="C600" t="s">
+        <v>521</v>
+      </c>
+      <c r="D600" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E600" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="s">
+        <v>145</v>
+      </c>
+      <c r="B601" t="s">
+        <v>435</v>
+      </c>
+      <c r="C601" t="s">
+        <v>521</v>
+      </c>
+      <c r="D601" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E601" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="s">
+        <v>145</v>
+      </c>
+      <c r="B602" t="s">
+        <v>435</v>
+      </c>
+      <c r="C602" t="s">
+        <v>521</v>
+      </c>
+      <c r="D602" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E602" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="s">
+        <v>145</v>
+      </c>
+      <c r="B603" t="s">
+        <v>435</v>
+      </c>
+      <c r="C603" t="s">
+        <v>521</v>
+      </c>
+      <c r="D603" t="s">
+        <v>61</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1238</v>
       </c>
     </row>
   </sheetData>
@@ -17460,13 +17672,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -17474,13 +17686,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -17488,13 +17700,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -17502,13 +17714,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -17516,13 +17728,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -17530,13 +17742,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -17544,13 +17756,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17558,13 +17770,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17572,13 +17784,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1238</v>
+        <v>1252</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1239</v>
+        <v>1253</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17596,13 +17808,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1240</v>
+        <v>1254</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17613,13 +17825,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1241</v>
+        <v>1255</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17630,13 +17842,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1242</v>
+        <v>1256</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17647,13 +17859,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1243</v>
+        <v>1257</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17664,13 +17876,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1244</v>
+        <v>1258</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17681,13 +17893,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17698,13 +17910,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1246</v>
+        <v>1260</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17715,13 +17927,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1247</v>
+        <v>1261</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17732,13 +17944,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1238</v>
+        <v>1252</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1248</v>
+        <v>1262</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="1263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1267">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3574 +207,3586 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-04-14</t>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
   </si>
   <si>
     <t>1254259.089613</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2024-01-12</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7406,7 +7418,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E603"/>
+  <dimension ref="A1:E606"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -17654,9 +17666,60 @@
         <v>521</v>
       </c>
       <c r="D603" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="s">
+        <v>145</v>
+      </c>
+      <c r="B604" t="s">
+        <v>435</v>
+      </c>
+      <c r="C604" t="s">
+        <v>521</v>
+      </c>
+      <c r="D604" t="s">
         <v>61</v>
       </c>
-      <c r="E603" t="s">
+      <c r="E604" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="s">
+        <v>104</v>
+      </c>
+      <c r="B605" t="s">
+        <v>435</v>
+      </c>
+      <c r="C605" t="s">
+        <v>521</v>
+      </c>
+      <c r="D605" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E605" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="s">
+        <v>104</v>
+      </c>
+      <c r="B606" t="s">
+        <v>435</v>
+      </c>
+      <c r="C606" t="s">
+        <v>521</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E606" t="s">
         <v>1238</v>
       </c>
     </row>
@@ -17672,13 +17735,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -17686,13 +17749,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -17700,13 +17763,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -17714,13 +17777,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -17728,13 +17791,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -17742,13 +17805,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -17756,13 +17819,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -17770,13 +17833,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -17784,13 +17847,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -17808,13 +17871,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -17825,13 +17888,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -17842,13 +17905,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -17859,13 +17922,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -17876,13 +17939,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -17893,13 +17956,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -17910,13 +17973,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -17927,13 +17990,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -17944,13 +18007,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1305">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3691 +207,3700 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-05-02</t>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
   </si>
   <si>
     <t>1280234.048113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7523,7 +7532,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E632"/>
+  <dimension ref="A1:E634"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18264,10 +18273,44 @@
         <v>521</v>
       </c>
       <c r="D632" t="s">
-        <v>61</v>
+        <v>1289</v>
       </c>
       <c r="E632" t="s">
         <v>1287</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="s">
+        <v>145</v>
+      </c>
+      <c r="B633" t="s">
+        <v>435</v>
+      </c>
+      <c r="C633" t="s">
+        <v>521</v>
+      </c>
+      <c r="D633" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E633" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="s">
+        <v>145</v>
+      </c>
+      <c r="B634" t="s">
+        <v>435</v>
+      </c>
+      <c r="C634" t="s">
+        <v>521</v>
+      </c>
+      <c r="D634" t="s">
+        <v>61</v>
+      </c>
+      <c r="E634" t="s">
+        <v>1291</v>
       </c>
     </row>
   </sheetData>
@@ -18282,13 +18325,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18296,13 +18339,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18310,13 +18353,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18324,13 +18367,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18338,13 +18381,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18352,13 +18395,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18366,13 +18409,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18380,13 +18423,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18394,13 +18437,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18418,13 +18461,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18435,13 +18478,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18452,13 +18495,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18469,13 +18512,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18486,13 +18529,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18503,13 +18546,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18520,13 +18563,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18537,13 +18580,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18554,13 +18597,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4240" uniqueCount="1309">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3700 +207,3712 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-05-03</t>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
   </si>
   <si>
     <t>1287034.048113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
     <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7532,7 +7544,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E634"/>
+  <dimension ref="A1:E636"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18307,10 +18319,44 @@
         <v>521</v>
       </c>
       <c r="D634" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E634" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="s">
+        <v>145</v>
+      </c>
+      <c r="B635" t="s">
+        <v>435</v>
+      </c>
+      <c r="C635" t="s">
+        <v>521</v>
+      </c>
+      <c r="D635" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E635" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="s">
+        <v>145</v>
+      </c>
+      <c r="B636" t="s">
+        <v>435</v>
+      </c>
+      <c r="C636" t="s">
+        <v>521</v>
+      </c>
+      <c r="D636" t="s">
         <v>61</v>
       </c>
-      <c r="E634" t="s">
-        <v>1291</v>
+      <c r="E636" t="s">
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -18325,13 +18371,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18339,13 +18385,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18353,13 +18399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18367,13 +18413,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18381,13 +18427,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18395,13 +18441,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18409,13 +18455,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18423,13 +18469,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18437,13 +18483,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18461,13 +18507,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18478,13 +18524,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18495,13 +18541,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18512,13 +18558,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18529,13 +18575,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18546,13 +18592,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18563,13 +18609,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18580,13 +18626,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18597,13 +18643,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4240" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="1317">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3712 +207,3736 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-05-05</t>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
   </si>
   <si>
     <t>1298037.048113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
     <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7544,7 +7568,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E636"/>
+  <dimension ref="A1:E641"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18353,10 +18377,95 @@
         <v>521</v>
       </c>
       <c r="D636" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E636" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B637" t="s">
+        <v>522</v>
+      </c>
+      <c r="C637" t="s">
+        <v>521</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E637" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="s">
+        <v>630</v>
+      </c>
+      <c r="B638" t="s">
+        <v>522</v>
+      </c>
+      <c r="C638" t="s">
+        <v>521</v>
+      </c>
+      <c r="D638" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E638" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="s">
+        <v>630</v>
+      </c>
+      <c r="B639" t="s">
+        <v>522</v>
+      </c>
+      <c r="C639" t="s">
+        <v>521</v>
+      </c>
+      <c r="D639" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E639" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="s">
+        <v>145</v>
+      </c>
+      <c r="B640" t="s">
+        <v>435</v>
+      </c>
+      <c r="C640" t="s">
+        <v>521</v>
+      </c>
+      <c r="D640" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E640" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="s">
+        <v>145</v>
+      </c>
+      <c r="B641" t="s">
+        <v>435</v>
+      </c>
+      <c r="C641" t="s">
+        <v>521</v>
+      </c>
+      <c r="D641" t="s">
         <v>61</v>
       </c>
-      <c r="E636" t="s">
-        <v>1295</v>
+      <c r="E641" t="s">
+        <v>1303</v>
       </c>
     </row>
   </sheetData>
@@ -18371,13 +18480,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18385,13 +18494,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18399,13 +18508,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18413,13 +18522,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18427,13 +18536,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18441,13 +18550,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18455,13 +18564,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18469,13 +18578,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18483,13 +18592,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18507,13 +18616,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18524,13 +18633,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18541,13 +18650,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18558,13 +18667,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18575,13 +18684,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18592,13 +18701,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18609,13 +18718,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18626,13 +18735,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18643,13 +18752,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4280" uniqueCount="1322">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3736 +207,3751 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-05-12</t>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
   </si>
   <si>
     <t>1298057.067113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7568,7 +7583,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E641"/>
+  <dimension ref="A1:E644"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18462,10 +18477,61 @@
         <v>521</v>
       </c>
       <c r="D641" t="s">
-        <v>61</v>
+        <v>1304</v>
       </c>
       <c r="E641" t="s">
         <v>1303</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="s">
+        <v>145</v>
+      </c>
+      <c r="B642" t="s">
+        <v>435</v>
+      </c>
+      <c r="C642" t="s">
+        <v>521</v>
+      </c>
+      <c r="D642" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E642" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B643" t="s">
+        <v>435</v>
+      </c>
+      <c r="C643" t="s">
+        <v>521</v>
+      </c>
+      <c r="D643" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E643" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B644" t="s">
+        <v>435</v>
+      </c>
+      <c r="C644" t="s">
+        <v>521</v>
+      </c>
+      <c r="D644" t="s">
+        <v>61</v>
+      </c>
+      <c r="E644" t="s">
+        <v>1308</v>
       </c>
     </row>
   </sheetData>
@@ -18480,13 +18546,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18494,13 +18560,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18508,13 +18574,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18522,13 +18588,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18536,13 +18602,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18550,13 +18616,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18564,13 +18630,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18578,13 +18644,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18592,13 +18658,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18616,13 +18682,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18633,13 +18699,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18650,13 +18716,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18667,13 +18733,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18684,13 +18750,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18701,13 +18767,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18718,13 +18784,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18735,13 +18801,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18752,13 +18818,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4280" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4305" uniqueCount="1330">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3751 +207,3775 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
     <t>2026-05-18</t>
   </si>
   <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7583,7 +7607,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E644"/>
+  <dimension ref="A1:E649"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18528,10 +18552,95 @@
         <v>521</v>
       </c>
       <c r="D644" t="s">
-        <v>61</v>
+        <v>1309</v>
       </c>
       <c r="E644" t="s">
         <v>1308</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="s">
+        <v>145</v>
+      </c>
+      <c r="B645" t="s">
+        <v>435</v>
+      </c>
+      <c r="C645" t="s">
+        <v>521</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E645" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="s">
+        <v>145</v>
+      </c>
+      <c r="B646" t="s">
+        <v>435</v>
+      </c>
+      <c r="C646" t="s">
+        <v>521</v>
+      </c>
+      <c r="D646" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E646" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="s">
+        <v>145</v>
+      </c>
+      <c r="B647" t="s">
+        <v>435</v>
+      </c>
+      <c r="C647" t="s">
+        <v>521</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E647" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="s">
+        <v>145</v>
+      </c>
+      <c r="B648" t="s">
+        <v>435</v>
+      </c>
+      <c r="C648" t="s">
+        <v>521</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E648" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="s">
+        <v>145</v>
+      </c>
+      <c r="B649" t="s">
+        <v>435</v>
+      </c>
+      <c r="C649" t="s">
+        <v>521</v>
+      </c>
+      <c r="D649" t="s">
+        <v>61</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1316</v>
       </c>
     </row>
   </sheetData>
@@ -18546,13 +18655,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18560,13 +18669,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18574,13 +18683,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18588,13 +18697,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18602,13 +18711,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18616,13 +18725,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18630,13 +18739,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18644,13 +18753,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18658,13 +18767,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18682,13 +18791,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18699,13 +18808,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18716,13 +18825,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18733,13 +18842,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18750,13 +18859,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18767,13 +18876,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18784,13 +18893,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18801,13 +18910,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18818,13 +18927,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4305" uniqueCount="1330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4330" uniqueCount="1339">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3775 +207,3802 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-05-26</t>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
   </si>
   <si>
     <t>1329797.067113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7607,7 +7634,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E649"/>
+  <dimension ref="A1:E654"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18637,10 +18664,95 @@
         <v>521</v>
       </c>
       <c r="D649" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="s">
+        <v>630</v>
+      </c>
+      <c r="B650" t="s">
+        <v>522</v>
+      </c>
+      <c r="C650" t="s">
+        <v>521</v>
+      </c>
+      <c r="D650" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E650" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="s">
+        <v>145</v>
+      </c>
+      <c r="B651" t="s">
+        <v>435</v>
+      </c>
+      <c r="C651" t="s">
+        <v>521</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E651" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="s">
+        <v>145</v>
+      </c>
+      <c r="B652" t="s">
+        <v>435</v>
+      </c>
+      <c r="C652" t="s">
+        <v>521</v>
+      </c>
+      <c r="D652" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="s">
+        <v>145</v>
+      </c>
+      <c r="B653" t="s">
+        <v>435</v>
+      </c>
+      <c r="C653" t="s">
+        <v>521</v>
+      </c>
+      <c r="D653" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E653" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="s">
+        <v>145</v>
+      </c>
+      <c r="B654" t="s">
+        <v>435</v>
+      </c>
+      <c r="C654" t="s">
+        <v>521</v>
+      </c>
+      <c r="D654" t="s">
         <v>61</v>
       </c>
-      <c r="E649" t="s">
-        <v>1316</v>
+      <c r="E654" t="s">
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -18655,13 +18767,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18669,13 +18781,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18683,13 +18795,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18697,13 +18809,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18711,13 +18823,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18725,13 +18837,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18739,13 +18851,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18753,13 +18865,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18767,13 +18879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18791,13 +18903,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18808,13 +18920,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1322</v>
+        <v>1331</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18825,13 +18937,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1323</v>
+        <v>1332</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18842,13 +18954,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1324</v>
+        <v>1333</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18859,13 +18971,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1325</v>
+        <v>1334</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18876,13 +18988,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1326</v>
+        <v>1335</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -18893,13 +19005,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -18910,13 +19022,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1328</v>
+        <v>1337</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -18927,13 +19039,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1329</v>
+        <v>1338</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4330" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="1358">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3802 +207,3859 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-06-09</t>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
   </si>
   <si>
     <t>1359441.467113</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
     <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7634,7 +7691,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E654"/>
+  <dimension ref="A1:E667"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18749,10 +18806,231 @@
         <v>521</v>
       </c>
       <c r="D654" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="s">
+        <v>690</v>
+      </c>
+      <c r="B655" t="s">
+        <v>522</v>
+      </c>
+      <c r="C655" t="s">
+        <v>521</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="s">
+        <v>690</v>
+      </c>
+      <c r="B656" t="s">
+        <v>522</v>
+      </c>
+      <c r="C656" t="s">
+        <v>521</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="s">
+        <v>690</v>
+      </c>
+      <c r="B657" t="s">
+        <v>522</v>
+      </c>
+      <c r="C657" t="s">
+        <v>521</v>
+      </c>
+      <c r="D657" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E657" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="s">
+        <v>690</v>
+      </c>
+      <c r="B658" t="s">
+        <v>522</v>
+      </c>
+      <c r="C658" t="s">
+        <v>521</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E658" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B659" t="s">
+        <v>522</v>
+      </c>
+      <c r="C659" t="s">
+        <v>521</v>
+      </c>
+      <c r="D659" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E659" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B660" t="s">
+        <v>522</v>
+      </c>
+      <c r="C660" t="s">
+        <v>521</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E660" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B661" t="s">
+        <v>522</v>
+      </c>
+      <c r="C661" t="s">
+        <v>521</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E661" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="s">
+        <v>90</v>
+      </c>
+      <c r="B662" t="s">
+        <v>522</v>
+      </c>
+      <c r="C662" t="s">
+        <v>521</v>
+      </c>
+      <c r="D662" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E662" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="s">
+        <v>90</v>
+      </c>
+      <c r="B663" t="s">
+        <v>522</v>
+      </c>
+      <c r="C663" t="s">
+        <v>521</v>
+      </c>
+      <c r="D663" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E663" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="s">
+        <v>90</v>
+      </c>
+      <c r="B664" t="s">
+        <v>522</v>
+      </c>
+      <c r="C664" t="s">
+        <v>521</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E664" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="s">
+        <v>145</v>
+      </c>
+      <c r="B665" t="s">
+        <v>435</v>
+      </c>
+      <c r="C665" t="s">
+        <v>521</v>
+      </c>
+      <c r="D665" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E665" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="s">
+        <v>145</v>
+      </c>
+      <c r="B666" t="s">
+        <v>435</v>
+      </c>
+      <c r="C666" t="s">
+        <v>521</v>
+      </c>
+      <c r="D666" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E666" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="s">
+        <v>145</v>
+      </c>
+      <c r="B667" t="s">
+        <v>435</v>
+      </c>
+      <c r="C667" t="s">
+        <v>521</v>
+      </c>
+      <c r="D667" t="s">
         <v>61</v>
       </c>
-      <c r="E654" t="s">
-        <v>1325</v>
+      <c r="E667" t="s">
+        <v>1344</v>
       </c>
     </row>
   </sheetData>
@@ -18767,13 +19045,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -18781,13 +19059,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -18795,13 +19073,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -18809,13 +19087,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -18823,13 +19101,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -18837,13 +19115,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -18851,13 +19129,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -18865,13 +19143,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -18879,13 +19157,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1329</v>
+        <v>1348</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -18903,13 +19181,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -18920,13 +19198,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -18937,13 +19215,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1332</v>
+        <v>1351</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -18954,13 +19232,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1333</v>
+        <v>1352</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -18971,13 +19249,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1334</v>
+        <v>1353</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -18988,13 +19266,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1335</v>
+        <v>1354</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -19005,13 +19283,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1336</v>
+        <v>1355</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -19022,13 +19300,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1337</v>
+        <v>1356</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -19039,13 +19317,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4430" uniqueCount="1368">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3859 +207,3889 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>1366885.426313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
   </si>
   <si>
     <t>1354862.276313</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
     <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7691,7 +7721,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E667"/>
+  <dimension ref="A1:E674"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -19027,10 +19057,129 @@
         <v>521</v>
       </c>
       <c r="D667" t="s">
-        <v>61</v>
+        <v>1344</v>
       </c>
       <c r="E667" t="s">
-        <v>1344</v>
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="s">
+        <v>145</v>
+      </c>
+      <c r="B668" t="s">
+        <v>435</v>
+      </c>
+      <c r="C668" t="s">
+        <v>521</v>
+      </c>
+      <c r="D668" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E668" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="s">
+        <v>145</v>
+      </c>
+      <c r="B669" t="s">
+        <v>435</v>
+      </c>
+      <c r="C669" t="s">
+        <v>521</v>
+      </c>
+      <c r="D669" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E669" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="s">
+        <v>145</v>
+      </c>
+      <c r="B670" t="s">
+        <v>435</v>
+      </c>
+      <c r="C670" t="s">
+        <v>521</v>
+      </c>
+      <c r="D670" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E670" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="s">
+        <v>145</v>
+      </c>
+      <c r="B671" t="s">
+        <v>435</v>
+      </c>
+      <c r="C671" t="s">
+        <v>521</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E671" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="s">
+        <v>145</v>
+      </c>
+      <c r="B672" t="s">
+        <v>435</v>
+      </c>
+      <c r="C672" t="s">
+        <v>521</v>
+      </c>
+      <c r="D672" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E672" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="s">
+        <v>145</v>
+      </c>
+      <c r="B673" t="s">
+        <v>435</v>
+      </c>
+      <c r="C673" t="s">
+        <v>521</v>
+      </c>
+      <c r="D673" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E673" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="s">
+        <v>145</v>
+      </c>
+      <c r="B674" t="s">
+        <v>435</v>
+      </c>
+      <c r="C674" t="s">
+        <v>521</v>
+      </c>
+      <c r="D674" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E674" t="s">
+        <v>1351</v>
       </c>
     </row>
   </sheetData>
@@ -19045,13 +19194,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -19059,13 +19208,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -19073,13 +19222,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -19087,13 +19236,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -19101,13 +19250,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -19115,13 +19264,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -19129,13 +19278,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -19143,13 +19292,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -19157,13 +19306,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -19181,13 +19330,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -19198,13 +19347,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -19215,13 +19364,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -19232,13 +19381,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -19249,13 +19398,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -19266,13 +19415,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -19283,13 +19432,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -19300,13 +19449,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -19317,13 +19466,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4535" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="1405">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,3976 +207,4000 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-07-14</t>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
   </si>
   <si>
     <t>1403968.073313</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7808,7 +7832,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E695"/>
+  <dimension ref="A1:E700"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -19620,10 +19644,95 @@
         <v>521</v>
       </c>
       <c r="D695" t="s">
-        <v>61</v>
+        <v>1384</v>
       </c>
       <c r="E695" t="s">
         <v>1383</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="s">
+        <v>690</v>
+      </c>
+      <c r="B696" t="s">
+        <v>522</v>
+      </c>
+      <c r="C696" t="s">
+        <v>521</v>
+      </c>
+      <c r="D696" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E696" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="s">
+        <v>630</v>
+      </c>
+      <c r="B697" t="s">
+        <v>522</v>
+      </c>
+      <c r="C697" t="s">
+        <v>521</v>
+      </c>
+      <c r="D697" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E697" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="s">
+        <v>145</v>
+      </c>
+      <c r="B698" t="s">
+        <v>435</v>
+      </c>
+      <c r="C698" t="s">
+        <v>521</v>
+      </c>
+      <c r="D698" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E698" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="s">
+        <v>145</v>
+      </c>
+      <c r="B699" t="s">
+        <v>435</v>
+      </c>
+      <c r="C699" t="s">
+        <v>521</v>
+      </c>
+      <c r="D699" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E699" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="s">
+        <v>145</v>
+      </c>
+      <c r="B700" t="s">
+        <v>435</v>
+      </c>
+      <c r="C700" t="s">
+        <v>521</v>
+      </c>
+      <c r="D700" t="s">
+        <v>61</v>
+      </c>
+      <c r="E700" t="s">
+        <v>1391</v>
       </c>
     </row>
   </sheetData>
@@ -19638,13 +19747,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -19652,13 +19761,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -19666,13 +19775,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -19680,13 +19789,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -19694,13 +19803,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -19708,13 +19817,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -19722,13 +19831,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -19736,13 +19845,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -19750,13 +19859,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -19774,13 +19883,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -19791,13 +19900,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -19808,13 +19917,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -19825,13 +19934,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -19842,13 +19951,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -19859,13 +19968,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -19876,13 +19985,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -19893,13 +20002,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -19910,13 +20019,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="1411">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4000 +207,4018 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-07-21</t>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
   </si>
   <si>
     <t>1410538.053813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7832,7 +7850,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E700"/>
+  <dimension ref="A1:E704"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -19729,10 +19747,78 @@
         <v>521</v>
       </c>
       <c r="D700" t="s">
-        <v>61</v>
+        <v>1392</v>
       </c>
       <c r="E700" t="s">
         <v>1391</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="s">
+        <v>90</v>
+      </c>
+      <c r="B701" t="s">
+        <v>522</v>
+      </c>
+      <c r="C701" t="s">
+        <v>521</v>
+      </c>
+      <c r="D701" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E701" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="s">
+        <v>145</v>
+      </c>
+      <c r="B702" t="s">
+        <v>435</v>
+      </c>
+      <c r="C702" t="s">
+        <v>521</v>
+      </c>
+      <c r="D702" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E702" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="s">
+        <v>145</v>
+      </c>
+      <c r="B703" t="s">
+        <v>435</v>
+      </c>
+      <c r="C703" t="s">
+        <v>521</v>
+      </c>
+      <c r="D703" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E703" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="s">
+        <v>145</v>
+      </c>
+      <c r="B704" t="s">
+        <v>435</v>
+      </c>
+      <c r="C704" t="s">
+        <v>521</v>
+      </c>
+      <c r="D704" t="s">
+        <v>61</v>
+      </c>
+      <c r="E704" t="s">
+        <v>1394</v>
       </c>
     </row>
   </sheetData>
@@ -19747,13 +19833,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -19761,13 +19847,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -19775,13 +19861,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -19789,13 +19875,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -19803,13 +19889,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -19817,13 +19903,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -19831,13 +19917,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -19845,13 +19931,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -19859,13 +19945,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -19883,13 +19969,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -19900,13 +19986,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -19917,13 +20003,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -19934,13 +20020,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -19951,13 +20037,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -19968,13 +20054,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -19985,13 +20071,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -20002,13 +20088,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -20019,13 +20105,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="1411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4630" uniqueCount="1423">
   <si>
     <t>car_insurance</t>
   </si>
@@ -210,4015 +210,4051 @@
     <t>2026-08-04</t>
   </si>
   <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
     <t>1416136.053813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7850,7 +7886,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E704"/>
+  <dimension ref="A1:E714"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -19815,10 +19851,180 @@
         <v>521</v>
       </c>
       <c r="D704" t="s">
-        <v>61</v>
+        <v>1398</v>
       </c>
       <c r="E704" t="s">
         <v>1394</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="s">
+        <v>145</v>
+      </c>
+      <c r="B705" t="s">
+        <v>435</v>
+      </c>
+      <c r="C705" t="s">
+        <v>521</v>
+      </c>
+      <c r="D705" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E705" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="s">
+        <v>145</v>
+      </c>
+      <c r="B706" t="s">
+        <v>435</v>
+      </c>
+      <c r="C706" t="s">
+        <v>521</v>
+      </c>
+      <c r="D706" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E706" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="s">
+        <v>145</v>
+      </c>
+      <c r="B707" t="s">
+        <v>435</v>
+      </c>
+      <c r="C707" t="s">
+        <v>521</v>
+      </c>
+      <c r="D707" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E707" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="s">
+        <v>145</v>
+      </c>
+      <c r="B708" t="s">
+        <v>435</v>
+      </c>
+      <c r="C708" t="s">
+        <v>521</v>
+      </c>
+      <c r="D708" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E708" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s">
+        <v>145</v>
+      </c>
+      <c r="B709" t="s">
+        <v>435</v>
+      </c>
+      <c r="C709" t="s">
+        <v>521</v>
+      </c>
+      <c r="D709" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E709" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="s">
+        <v>145</v>
+      </c>
+      <c r="B710" t="s">
+        <v>435</v>
+      </c>
+      <c r="C710" t="s">
+        <v>521</v>
+      </c>
+      <c r="D710" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E710" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="s">
+        <v>145</v>
+      </c>
+      <c r="B711" t="s">
+        <v>435</v>
+      </c>
+      <c r="C711" t="s">
+        <v>521</v>
+      </c>
+      <c r="D711" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E711" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="s">
+        <v>145</v>
+      </c>
+      <c r="B712" t="s">
+        <v>435</v>
+      </c>
+      <c r="C712" t="s">
+        <v>521</v>
+      </c>
+      <c r="D712" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E712" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="s">
+        <v>145</v>
+      </c>
+      <c r="B713" t="s">
+        <v>435</v>
+      </c>
+      <c r="C713" t="s">
+        <v>521</v>
+      </c>
+      <c r="D713" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E713" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="s">
+        <v>145</v>
+      </c>
+      <c r="B714" t="s">
+        <v>435</v>
+      </c>
+      <c r="C714" t="s">
+        <v>521</v>
+      </c>
+      <c r="D714" t="s">
+        <v>61</v>
+      </c>
+      <c r="E714" t="s">
+        <v>1409</v>
       </c>
     </row>
   </sheetData>
@@ -19833,13 +20039,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -19847,13 +20053,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -19861,13 +20067,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -19875,13 +20081,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -19889,13 +20095,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -19903,13 +20109,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -19917,13 +20123,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -19931,13 +20137,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -19945,13 +20151,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1401</v>
+        <v>1413</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -19969,13 +20175,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1402</v>
+        <v>1414</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -19986,13 +20192,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1403</v>
+        <v>1415</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -20003,13 +20209,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1404</v>
+        <v>1416</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -20020,13 +20226,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1405</v>
+        <v>1417</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -20037,13 +20243,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1406</v>
+        <v>1418</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -20054,13 +20260,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1407</v>
+        <v>1419</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -20071,13 +20277,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1408</v>
+        <v>1420</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -20088,13 +20294,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1409</v>
+        <v>1421</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -20105,13 +20311,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -207,7 +207,7 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-08-04</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>1444916.753813</t>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4630" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4690" uniqueCount="1437">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4054 +207,4096 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-08-07</t>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
   </si>
   <si>
     <t>1444916.753813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7886,7 +7928,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E714"/>
+  <dimension ref="A1:E726"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -20021,10 +20063,214 @@
         <v>521</v>
       </c>
       <c r="D714" t="s">
-        <v>61</v>
+        <v>1410</v>
       </c>
       <c r="E714" t="s">
         <v>1409</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="s">
+        <v>630</v>
+      </c>
+      <c r="B715" t="s">
+        <v>522</v>
+      </c>
+      <c r="C715" t="s">
+        <v>521</v>
+      </c>
+      <c r="D715" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E715" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="s">
+        <v>630</v>
+      </c>
+      <c r="B716" t="s">
+        <v>522</v>
+      </c>
+      <c r="C716" t="s">
+        <v>521</v>
+      </c>
+      <c r="D716" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E716" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="s">
+        <v>630</v>
+      </c>
+      <c r="B717" t="s">
+        <v>522</v>
+      </c>
+      <c r="C717" t="s">
+        <v>521</v>
+      </c>
+      <c r="D717" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E717" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="s">
+        <v>630</v>
+      </c>
+      <c r="B718" t="s">
+        <v>522</v>
+      </c>
+      <c r="C718" t="s">
+        <v>521</v>
+      </c>
+      <c r="D718" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E718" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="s">
+        <v>145</v>
+      </c>
+      <c r="B719" t="s">
+        <v>435</v>
+      </c>
+      <c r="C719" t="s">
+        <v>521</v>
+      </c>
+      <c r="D719" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E719" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="s">
+        <v>145</v>
+      </c>
+      <c r="B720" t="s">
+        <v>435</v>
+      </c>
+      <c r="C720" t="s">
+        <v>521</v>
+      </c>
+      <c r="D720" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E720" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="s">
+        <v>145</v>
+      </c>
+      <c r="B721" t="s">
+        <v>435</v>
+      </c>
+      <c r="C721" t="s">
+        <v>521</v>
+      </c>
+      <c r="D721" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E721" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="s">
+        <v>145</v>
+      </c>
+      <c r="B722" t="s">
+        <v>435</v>
+      </c>
+      <c r="C722" t="s">
+        <v>521</v>
+      </c>
+      <c r="D722" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E722" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="s">
+        <v>145</v>
+      </c>
+      <c r="B723" t="s">
+        <v>435</v>
+      </c>
+      <c r="C723" t="s">
+        <v>521</v>
+      </c>
+      <c r="D723" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E723" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="s">
+        <v>145</v>
+      </c>
+      <c r="B724" t="s">
+        <v>435</v>
+      </c>
+      <c r="C724" t="s">
+        <v>521</v>
+      </c>
+      <c r="D724" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E724" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="s">
+        <v>145</v>
+      </c>
+      <c r="B725" t="s">
+        <v>435</v>
+      </c>
+      <c r="C725" t="s">
+        <v>521</v>
+      </c>
+      <c r="D725" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E725" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="s">
+        <v>145</v>
+      </c>
+      <c r="B726" t="s">
+        <v>435</v>
+      </c>
+      <c r="C726" t="s">
+        <v>521</v>
+      </c>
+      <c r="D726" t="s">
+        <v>61</v>
+      </c>
+      <c r="E726" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -20039,13 +20285,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -20053,13 +20299,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -20067,13 +20313,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -20081,13 +20327,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -20095,13 +20341,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -20109,13 +20355,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -20123,13 +20369,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -20137,13 +20383,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -20151,13 +20397,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1412</v>
+        <v>1426</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1413</v>
+        <v>1427</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -20175,13 +20421,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1414</v>
+        <v>1428</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -20192,13 +20438,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -20209,13 +20455,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1416</v>
+        <v>1430</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -20226,13 +20472,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1417</v>
+        <v>1431</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -20243,13 +20489,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1418</v>
+        <v>1432</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -20260,13 +20506,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1419</v>
+        <v>1433</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -20277,13 +20523,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1420</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -20294,13 +20540,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1421</v>
+        <v>1435</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -20311,13 +20557,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1412</v>
+        <v>1426</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1422</v>
+        <v>1436</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4690" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4720" uniqueCount="1446">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4096 +207,4123 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
     <t>2026-08-10</t>
   </si>
   <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
     <t>1457482.753813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
   </si>
   <si>
     <t>arpit</t>
@@ -7928,7 +7955,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E726"/>
+  <dimension ref="A1:E732"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -20236,7 +20263,7 @@
         <v>1422</v>
       </c>
       <c r="E724" t="s">
-        <v>60</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="725">
@@ -20250,10 +20277,10 @@
         <v>521</v>
       </c>
       <c r="D725" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E725" t="s">
         <v>1423</v>
-      </c>
-      <c r="E725" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="726">
@@ -20267,10 +20294,112 @@
         <v>521</v>
       </c>
       <c r="D726" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E726" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="s">
+        <v>630</v>
+      </c>
+      <c r="B727" t="s">
+        <v>522</v>
+      </c>
+      <c r="C727" t="s">
+        <v>521</v>
+      </c>
+      <c r="D727" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E727" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="s">
+        <v>145</v>
+      </c>
+      <c r="B728" t="s">
+        <v>435</v>
+      </c>
+      <c r="C728" t="s">
+        <v>521</v>
+      </c>
+      <c r="D728" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E728" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="s">
+        <v>145</v>
+      </c>
+      <c r="B729" t="s">
+        <v>435</v>
+      </c>
+      <c r="C729" t="s">
+        <v>521</v>
+      </c>
+      <c r="D729" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E729" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="s">
+        <v>145</v>
+      </c>
+      <c r="B730" t="s">
+        <v>435</v>
+      </c>
+      <c r="C730" t="s">
+        <v>521</v>
+      </c>
+      <c r="D730" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E730" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="s">
+        <v>145</v>
+      </c>
+      <c r="B731" t="s">
+        <v>435</v>
+      </c>
+      <c r="C731" t="s">
+        <v>521</v>
+      </c>
+      <c r="D731" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E731" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="s">
+        <v>145</v>
+      </c>
+      <c r="B732" t="s">
+        <v>435</v>
+      </c>
+      <c r="C732" t="s">
+        <v>521</v>
+      </c>
+      <c r="D732" t="s">
         <v>61</v>
       </c>
-      <c r="E726" t="s">
-        <v>60</v>
+      <c r="E732" t="s">
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -20285,13 +20414,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -20299,13 +20428,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -20313,13 +20442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -20327,13 +20456,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -20341,13 +20470,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -20355,13 +20484,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -20369,13 +20498,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -20383,13 +20512,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -20397,13 +20526,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1427</v>
+        <v>1436</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -20421,13 +20550,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1428</v>
+        <v>1437</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -20438,13 +20567,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1429</v>
+        <v>1438</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -20455,13 +20584,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1430</v>
+        <v>1439</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -20472,13 +20601,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1431</v>
+        <v>1440</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -20489,13 +20618,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1432</v>
+        <v>1441</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -20506,13 +20635,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -20523,13 +20652,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -20540,13 +20669,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -20557,13 +20686,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1436</v>
+        <v>1445</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -207,7 +207,7 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-08-15</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>1466302.752313</t>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4720" uniqueCount="1446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="1454">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4123 +207,4147 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-08-18</t>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
